--- a/processo_2/synthetic_proposals/PROPOSTA_034/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_034/ficha_pontuacao.xlsx
@@ -680,17 +680,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
@@ -703,17 +703,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr"/>
     </row>
@@ -726,17 +726,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -973,17 +973,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr"/>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1067,7 +1067,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1225,17 +1225,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G39" t="inlineStr"/>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>1.5</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G42" t="inlineStr"/>
     </row>
@@ -1317,17 +1317,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>1.5</v>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr"/>
     </row>
@@ -1384,13 +1384,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>6</v>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G46" t="inlineStr"/>
     </row>
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr"/>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1604,17 +1604,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G56" t="inlineStr"/>
     </row>
@@ -1627,17 +1627,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
         <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G57" t="inlineStr"/>
     </row>
@@ -1652,7 +1652,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>30</v>
+        <v>7.5</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
         <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G62" t="inlineStr"/>
     </row>
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>4</v>
       </c>
       <c r="F63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G63" t="inlineStr"/>
     </row>
@@ -1835,7 +1835,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
@@ -1850,7 +1850,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
